--- a/data/calibrations/décomposition coûts électricité.xlsx
+++ b/data/calibrations/décomposition coûts électricité.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\callonnecg\Documents\Github\ThreeME\data\calibrations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ThreeME\data\calibrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FDDE5E-AF61-4BA0-8BB1-E04BFC1CBC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3147C8-CEAE-4B92-A3FC-3F330B6C4A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="10" xr2:uid="{CD40A21A-F6E4-4FAF-9044-22292F8CEF96}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{CD40A21A-F6E4-4FAF-9044-22292F8CEF96}"/>
   </bookViews>
   <sheets>
     <sheet name="CoutMwh" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
-    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
     <definedName name="_ftn1" localSheetId="3">'coût S2'!$A$161</definedName>
@@ -2338,6 +2337,24 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="26" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2356,23 +2373,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2390,9 +2392,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2755,253 +2754,6 @@
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cibles THREEME"/>
-      <sheetName val="Cibles THREEME AMS"/>
-      <sheetName val="Cibles ThreeME v2 "/>
-      <sheetName val="Cibles ThreeME v2 AMS"/>
-      <sheetName val="Cibles ThreeME v3"/>
-      <sheetName val="Cibles ThreeME v3 AMS"/>
-      <sheetName val="brouillon"/>
-      <sheetName val="Bilan_enerdata_2015"/>
-      <sheetName val="Bilan 2015"/>
-      <sheetName val="Bilan 2020"/>
-      <sheetName val="Bilan 2020 test"/>
-      <sheetName val="Bilan 2023"/>
-      <sheetName val="Bilan 2025"/>
-      <sheetName val="Bilan 2028"/>
-      <sheetName val="Bilan 2030"/>
-      <sheetName val="Bilan 2033"/>
-      <sheetName val="Bilan 2035"/>
-      <sheetName val="Bilan 2038"/>
-      <sheetName val="Bilan 2040"/>
-      <sheetName val="Bilan 2045"/>
-      <sheetName val="Bilan 2050"/>
-      <sheetName val="Bilan 2023 AMS"/>
-      <sheetName val="Bilan 2025 AMS"/>
-      <sheetName val="Bilan 2028 AMS"/>
-      <sheetName val="Bilan 2030 AMS"/>
-      <sheetName val="Bilan 2033 AMS"/>
-      <sheetName val="Bilan 2035 AMS"/>
-      <sheetName val="Bilan 2038 AMS"/>
-      <sheetName val="Bilan 2040 AMS"/>
-      <sheetName val="Bilan 2045 AMS"/>
-      <sheetName val="Bilan 2050 AMS"/>
-      <sheetName val="Bilan_E_AME_Met_2020"/>
-      <sheetName val="Bilan_E_KP_AME_2020"/>
-      <sheetName val="Bilan_E_KP_AME_2023"/>
-      <sheetName val="Bilan_E_KP_AME_2025"/>
-      <sheetName val="Bilan_E_KP_AME_2028"/>
-      <sheetName val="Bilan_E_KP_AME_2030"/>
-      <sheetName val="Bilan_E_KP_AME_2033"/>
-      <sheetName val="Bilan_E_KP_AME_2035"/>
-      <sheetName val="Bilan_E_KP_AME_2038"/>
-      <sheetName val="Bilan_E_KP_AME_2040"/>
-      <sheetName val="Bilan_E_KP_AME_2043"/>
-      <sheetName val="Bilan_E_KP_AME_2045"/>
-      <sheetName val="Bilan_E_KP_AME_2050"/>
-      <sheetName val="Bilan_E_KP_AME"/>
-      <sheetName val="Bilans_E_AMS_KP"/>
-      <sheetName val="Bilans_E_AMS_KP_2023"/>
-      <sheetName val="Bilans_E_AMS_KP_2025"/>
-      <sheetName val="Bilans_E_AMS_KP_2028"/>
-      <sheetName val="Bilans_E_AMS_KP_2030"/>
-      <sheetName val="Bilans_E_AMS_KP_2033"/>
-      <sheetName val="Bilans_E_AMS_KP_2035"/>
-      <sheetName val="Bilans_E_AMS_KP_2038"/>
-      <sheetName val="Bilans_E_AMS_KP_2040"/>
-      <sheetName val="Bilans_E_AMS_KP_2043"/>
-      <sheetName val="Bilans_E_AMS_KP_2045"/>
-      <sheetName val="Bilans_E_AMS_KP_2050"/>
-      <sheetName val="Bilan_E_KP_AMS_2023"/>
-      <sheetName val="Bilan_E_KP_AMS_2025"/>
-      <sheetName val="Bilan_E_KP_AMS_2028"/>
-      <sheetName val="Bilan_E_KP_AMS_2030"/>
-      <sheetName val="Bilan_E_KP_AMS_2033"/>
-      <sheetName val="Bilan_E_KP_AMS_2035"/>
-      <sheetName val="Bilan_E_KP_AMS_2038"/>
-      <sheetName val="Bilan_E_KP_AMS_2040"/>
-      <sheetName val="Bilan_E_KP_AMS_2043"/>
-      <sheetName val="Bilan_E_KP_AMS_2045"/>
-      <sheetName val="Bilan_E_KP_AMS_2050"/>
-      <sheetName val="Bilan_E_KP_AMS"/>
-      <sheetName val="P1_G4-G5"/>
-      <sheetName val="P1_G6"/>
-      <sheetName val="bilan énergie format SDS"/>
-      <sheetName val="Demande Format Medpro"/>
-      <sheetName val="Format demande MedPro_2015"/>
-      <sheetName val="Corrections Bilan enerdata"/>
-      <sheetName val="Modèle tertiaire_2015"/>
-      <sheetName val="Modèle tertiaire_2020"/>
-      <sheetName val="Modèle tertiaire_2025"/>
-      <sheetName val="Modèle tertiaire_2030"/>
-      <sheetName val="Modèle tertiaire_2050"/>
-      <sheetName val="Modèle résidentiel ch_2015"/>
-      <sheetName val="Modèle résidentiel ch_2020"/>
-      <sheetName val="Modèle résidentiel ch_2025"/>
-      <sheetName val="Modèle résidentiel ch_2030"/>
-      <sheetName val="Modèle résidentiel ch_2050"/>
-      <sheetName val="Modèle résidentiel hch_2015"/>
-      <sheetName val="Modèle résidentiel hch_2020"/>
-      <sheetName val="Modèle résidentiel hch_2025"/>
-      <sheetName val="Modèle résidentiel hch_2030"/>
-      <sheetName val="Modèle résidentiel hch_2050"/>
-      <sheetName val="Mix énergie_2015"/>
-      <sheetName val="Bilans_E_AMS_Kyoto_2050"/>
-      <sheetName val="Bilan 2050 AMS_ancien"/>
-      <sheetName val="Bilans_E_AMS_Kyoto"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="7">
-          <cell r="I7">
-            <v>24.904679182551273</v>
-          </cell>
-          <cell r="N7">
-            <v>7.6163243247728092</v>
-          </cell>
-          <cell r="S7">
-            <v>7.5523881054869557</v>
-          </cell>
-          <cell r="X7">
-            <v>7.9623342705743987</v>
-          </cell>
-          <cell r="AC7">
-            <v>8.315170606453826</v>
-          </cell>
-          <cell r="AH7">
-            <v>8.579895509379492</v>
-          </cell>
-          <cell r="AM7">
-            <v>24.603178920457438</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="7">
-          <cell r="N7">
-            <v>26.434633696901958</v>
-          </cell>
-          <cell r="S7">
-            <v>23.012014275261006</v>
-          </cell>
-          <cell r="X7">
-            <v>17.076239626292423</v>
-          </cell>
-          <cell r="AC7">
-            <v>1.9497760583305019</v>
-          </cell>
-          <cell r="AH7">
-            <v>2.6500221012566496</v>
-          </cell>
-          <cell r="AM7">
-            <v>3.1772529313232827</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70"/>
-      <sheetData sheetId="71"/>
-      <sheetData sheetId="72"/>
-      <sheetData sheetId="73"/>
-      <sheetData sheetId="74"/>
-      <sheetData sheetId="75"/>
-      <sheetData sheetId="76"/>
-      <sheetData sheetId="77"/>
-      <sheetData sheetId="78"/>
-      <sheetData sheetId="79"/>
-      <sheetData sheetId="80"/>
-      <sheetData sheetId="81"/>
-      <sheetData sheetId="82"/>
-      <sheetData sheetId="83"/>
-      <sheetData sheetId="84"/>
-      <sheetData sheetId="85"/>
-      <sheetData sheetId="86"/>
-      <sheetData sheetId="87"/>
-      <sheetData sheetId="88"/>
-      <sheetData sheetId="89"/>
-      <sheetData sheetId="90"/>
-      <sheetData sheetId="91"/>
-      <sheetData sheetId="92"/>
-      <sheetData sheetId="93"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Confidentialité"/>
       <sheetName val="Investissements"/>
@@ -3615,13 +3367,15 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="technical_coef_var_ams2"/>
+      <sheetName val="technical_coef_var_ams"/>
       <sheetName val="Legend"/>
       <sheetName val="BaselineHypotheses"/>
       <sheetName val="Supply_Use_dom"/>
@@ -3659,39 +3413,41 @@
       <sheetName val="M_footprint"/>
       <sheetName val="imports"/>
       <sheetName val="ThreeME V1_V2"/>
-      <sheetName val="technical_coef_variation"/>
-      <sheetName val="technical_coef_variation_2"/>
+      <sheetName val="technical_coef_var"/>
+      <sheetName val="technical_coef_var_2"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28">
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30">
         <row r="48">
           <cell r="F48">
             <v>18.979902880269496</v>
@@ -3757,22 +3513,22 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4577,17 +4333,16 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cibles THREEME"/>
+      <sheetName val="Cibles ThreeME v2 "/>
+      <sheetName val=" fonds chaleur"/>
       <sheetName val="Cibles THREEME AMS"/>
-      <sheetName val="Cibles ThreeME v2 "/>
       <sheetName val="Cibles ThreeME v2 AMS"/>
+      <sheetName val="Cibles ThreeME v2 AMS FC"/>
       <sheetName val="Cibles ThreeME v3"/>
       <sheetName val="Cibles ThreeME v3 AMS"/>
       <sheetName val="brouillon"/>
@@ -4595,6 +4350,8 @@
       <sheetName val="Bilan 2015"/>
       <sheetName val="Bilan 2020"/>
       <sheetName val="Bilan 2020 test"/>
+      <sheetName val="Bilan 2022 réel"/>
+      <sheetName val="Bilan 2023 réel"/>
       <sheetName val="Bilan 2023"/>
       <sheetName val="Bilan 2025"/>
       <sheetName val="Bilan 2028"/>
@@ -4615,6 +4372,8 @@
       <sheetName val="Bilan 2040 AMS"/>
       <sheetName val="Bilan 2045 AMS"/>
       <sheetName val="Bilan 2050 AMS"/>
+      <sheetName val="Bilan_E_KP_réel_2022"/>
+      <sheetName val="Bilan_E_KP_réel_2023"/>
       <sheetName val="Bilan_E_AME_Met_2020"/>
       <sheetName val="Bilan_E_KP_AME_2020"/>
       <sheetName val="Bilan_E_KP_AME_2023"/>
@@ -4678,11 +4437,34 @@
       <sheetName val="Bilans_E_AMS_Kyoto_2050"/>
       <sheetName val="Bilan 2050 AMS_ancien"/>
       <sheetName val="Bilans_E_AMS_Kyoto"/>
+      <sheetName val="Bilan énergie - AMErun2 - AMSru"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="1">
+        <row r="7">
+          <cell r="I7">
+            <v>24.904679182551273</v>
+          </cell>
+          <cell r="N7">
+            <v>7.6163243247728092</v>
+          </cell>
+          <cell r="S7">
+            <v>7.5523881054869557</v>
+          </cell>
+          <cell r="X7">
+            <v>7.9623342705743987</v>
+          </cell>
+          <cell r="AC7">
+            <v>8.315170606453826</v>
+          </cell>
+          <cell r="AH7">
+            <v>8.579895509379492</v>
+          </cell>
+          <cell r="AM7">
+            <v>24.603178920457438</v>
+          </cell>
+        </row>
         <row r="12">
           <cell r="N12">
             <v>9.9244961880322116</v>
@@ -4704,7 +4486,29 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="7">
+          <cell r="N7">
+            <v>26.434633696901958</v>
+          </cell>
+          <cell r="S7">
+            <v>23.012014275261006</v>
+          </cell>
+          <cell r="X7">
+            <v>17.076239626292423</v>
+          </cell>
+          <cell r="AC7">
+            <v>1.9497760583305019</v>
+          </cell>
+          <cell r="AH7">
+            <v>2.6500221012566496</v>
+          </cell>
+          <cell r="AM7">
+            <v>3.1772529313232827</v>
+          </cell>
+        </row>
         <row r="12">
           <cell r="I12">
             <v>4.9342958979932492</v>
@@ -4729,7 +4533,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
@@ -4819,6 +4622,13 @@
       <sheetData sheetId="91"/>
       <sheetData sheetId="92"/>
       <sheetData sheetId="93"/>
+      <sheetData sheetId="94"/>
+      <sheetData sheetId="95"/>
+      <sheetData sheetId="96"/>
+      <sheetData sheetId="97"/>
+      <sheetData sheetId="98"/>
+      <sheetData sheetId="99"/>
+      <sheetData sheetId="100" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5122,7 +4932,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="104" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -5157,7 +4967,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="111"/>
+      <c r="A3" s="105"/>
       <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
@@ -5190,7 +5000,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="112"/>
+      <c r="A4" s="106"/>
       <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
@@ -5223,7 +5033,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="107" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -5258,7 +5068,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="114"/>
+      <c r="A6" s="108"/>
       <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
@@ -5291,7 +5101,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="115"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
@@ -5324,7 +5134,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="104" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -5359,7 +5169,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="111"/>
+      <c r="A9" s="105"/>
       <c r="B9" s="6" t="s">
         <v>2</v>
       </c>
@@ -5392,7 +5202,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="112"/>
+      <c r="A10" s="106"/>
       <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
@@ -5425,7 +5235,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="113" t="s">
+      <c r="A11" s="107" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -5460,7 +5270,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="114"/>
+      <c r="A12" s="108"/>
       <c r="B12" s="6" t="s">
         <v>2</v>
       </c>
@@ -5493,7 +5303,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="115"/>
+      <c r="A13" s="109"/>
       <c r="B13" s="6" t="s">
         <v>3</v>
       </c>
@@ -5526,7 +5336,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="104" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -5561,7 +5371,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="111"/>
+      <c r="A15" s="105"/>
       <c r="B15" s="6" t="s">
         <v>2</v>
       </c>
@@ -5594,7 +5404,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112"/>
+      <c r="A16" s="106"/>
       <c r="B16" s="6" t="s">
         <v>3</v>
       </c>
@@ -5732,7 +5542,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="104" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -5767,7 +5577,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="111"/>
+      <c r="A21" s="105"/>
       <c r="B21" s="6" t="s">
         <v>2</v>
       </c>
@@ -5800,7 +5610,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="111"/>
+      <c r="A22" s="105"/>
       <c r="B22" s="12" t="s">
         <v>3</v>
       </c>
@@ -5833,7 +5643,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="108" t="s">
+      <c r="A23" s="114" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -5876,7 +5686,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="109" t="s">
+      <c r="A24" s="115" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -5919,7 +5729,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="109"/>
+      <c r="A25" s="115"/>
       <c r="B25" s="12" t="s">
         <v>18</v>
       </c>
@@ -5960,7 +5770,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="109"/>
+      <c r="A26" s="115"/>
       <c r="B26" s="6" t="s">
         <v>19</v>
       </c>
@@ -6001,7 +5811,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="109"/>
+      <c r="A27" s="115"/>
       <c r="B27" s="6" t="s">
         <v>21</v>
       </c>
@@ -6057,7 +5867,7 @@
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="108" t="s">
+      <c r="A29" s="114" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -6100,7 +5910,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="109" t="s">
+      <c r="A30" s="115" t="s">
         <v>15</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -6143,7 +5953,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="109"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="12" t="s">
         <v>18</v>
       </c>
@@ -6184,7 +5994,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="109"/>
+      <c r="A32" s="115"/>
       <c r="B32" s="6" t="s">
         <v>19</v>
       </c>
@@ -6225,7 +6035,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="109"/>
+      <c r="A33" s="115"/>
       <c r="B33" s="6" t="s">
         <v>21</v>
       </c>
@@ -6287,7 +6097,7 @@
       <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="104" t="s">
+      <c r="A35" s="110" t="s">
         <v>29</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -6322,7 +6132,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="105"/>
+      <c r="A36" s="111"/>
       <c r="B36" s="6" t="s">
         <v>30</v>
       </c>
@@ -6355,7 +6165,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="105"/>
+      <c r="A37" s="111"/>
       <c r="B37" s="12" t="s">
         <v>31</v>
       </c>
@@ -6388,7 +6198,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="106"/>
+      <c r="A38" s="112"/>
       <c r="B38" s="6" t="s">
         <v>3</v>
       </c>
@@ -6421,7 +6231,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="107" t="s">
+      <c r="A39" s="113" t="s">
         <v>32</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -6456,7 +6266,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="105"/>
+      <c r="A40" s="111"/>
       <c r="B40" s="6" t="s">
         <v>30</v>
       </c>
@@ -6489,7 +6299,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="6" t="s">
         <v>33</v>
       </c>
@@ -6522,7 +6332,7 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="106"/>
+      <c r="A42" s="112"/>
       <c r="B42" s="6" t="s">
         <v>3</v>
       </c>
@@ -6584,18 +6394,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A33"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" location="_ftn1" display="_ftn1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6927,11 +6737,11 @@
         <v>67.416799999999995</v>
       </c>
       <c r="H3" s="69">
-        <f>'[5]CU énergie'!$F49*0.1</f>
+        <f>'[4]CU énergie'!$F49*0.1</f>
         <v>12.2576</v>
       </c>
       <c r="I3" s="69">
-        <f t="shared" ref="I3:L9" si="7">H3+($M3-$H3)/5</f>
+        <f t="shared" ref="I3:L8" si="7">H3+($M3-$H3)/5</f>
         <v>12.2576</v>
       </c>
       <c r="J3" s="69">
@@ -6947,11 +6757,11 @@
         <v>12.2576</v>
       </c>
       <c r="M3" s="69">
-        <f>'[5]CU énergie'!$F49*0.1</f>
+        <f>'[4]CU énergie'!$F49*0.1</f>
         <v>12.2576</v>
       </c>
       <c r="N3" s="69">
-        <f t="shared" ref="N3:Q9" si="8">M3+($R3-$M3)/5</f>
+        <f t="shared" ref="N3:Q8" si="8">M3+($R3-$M3)/5</f>
         <v>12.2576</v>
       </c>
       <c r="O3" s="69">
@@ -6967,11 +6777,11 @@
         <v>12.2576</v>
       </c>
       <c r="R3" s="69">
-        <f>'[5]CU énergie'!$F49*0.1</f>
+        <f>'[4]CU énergie'!$F49*0.1</f>
         <v>12.2576</v>
       </c>
       <c r="S3" s="69">
-        <f t="shared" ref="S3:V9" si="9">R3+($W3-$R3)/5</f>
+        <f t="shared" ref="S3:V8" si="9">R3+($W3-$R3)/5</f>
         <v>12.2576</v>
       </c>
       <c r="T3" s="69">
@@ -6987,11 +6797,11 @@
         <v>12.2576</v>
       </c>
       <c r="W3" s="69">
-        <f>'[5]CU énergie'!$F49*0.1</f>
+        <f>'[4]CU énergie'!$F49*0.1</f>
         <v>12.2576</v>
       </c>
       <c r="X3" s="69">
-        <f t="shared" ref="X3:AA9" si="10">W3+($AB3-$W3)/5</f>
+        <f t="shared" ref="X3:AA8" si="10">W3+($AB3-$W3)/5</f>
         <v>12.2576</v>
       </c>
       <c r="Y3" s="69">
@@ -7007,11 +6817,11 @@
         <v>12.2576</v>
       </c>
       <c r="AB3" s="69">
-        <f>'[5]CU énergie'!$F49*0.1</f>
+        <f>'[4]CU énergie'!$F49*0.1</f>
         <v>12.2576</v>
       </c>
       <c r="AC3" s="69">
-        <f t="shared" ref="AC3:AF9" si="11">AB3+($AG3-$AB3)/5</f>
+        <f t="shared" ref="AC3:AF8" si="11">AB3+($AG3-$AB3)/5</f>
         <v>12.2576</v>
       </c>
       <c r="AD3" s="69">
@@ -7027,7 +6837,7 @@
         <v>12.2576</v>
       </c>
       <c r="AG3" s="69">
-        <f>'[5]CU énergie'!$F49*0.1</f>
+        <f>'[4]CU énergie'!$F49*0.1</f>
         <v>12.2576</v>
       </c>
       <c r="AH3" s="41"/>
@@ -7235,107 +7045,107 @@
         <v>78.757822568760332</v>
       </c>
       <c r="H5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="I5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="J5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="K5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="L5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="M5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="N5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="O5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="P5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="Q5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="R5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="S5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="T5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="U5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="V5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="W5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="X5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="Y5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="Z5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AA5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AB5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AC5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AD5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AE5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AF5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AG5" s="69">
-        <f>'[5]CU énergie'!$F51*1</f>
+        <f>'[4]CU énergie'!$F51*1</f>
         <v>14.31960410341097</v>
       </c>
       <c r="AH5" s="41"/>
@@ -7697,7 +7507,7 @@
         <v>40298.281210297966</v>
       </c>
       <c r="H8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût S2'!D128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût S2'!D128*40</f>
         <v>40429.342043787678</v>
       </c>
       <c r="I8" s="69">
@@ -7717,7 +7527,7 @@
         <v>41375.160252137634</v>
       </c>
       <c r="M8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût S2'!E128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût S2'!E128*40</f>
         <v>41611.61480422513</v>
       </c>
       <c r="N8" s="69">
@@ -7737,7 +7547,7 @@
         <v>41612.615832432668</v>
       </c>
       <c r="R8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût S2'!F128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût S2'!F128*40</f>
         <v>41612.86608948456</v>
       </c>
       <c r="S8" s="69">
@@ -7757,7 +7567,7 @@
         <v>41943.107809496803</v>
       </c>
       <c r="W8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût S2'!G128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût S2'!G128*40</f>
         <v>42025.668239499864</v>
       </c>
       <c r="X8" s="69">
@@ -7777,7 +7587,7 @@
         <v>42135.619681379278</v>
       </c>
       <c r="AB8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût S2'!H128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût S2'!H128*40</f>
         <v>42163.107541849138</v>
       </c>
       <c r="AC8" s="69">
@@ -7797,7 +7607,7 @@
         <v>42073.552733430901</v>
       </c>
       <c r="AG8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût S2'!I128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût S2'!I128*40</f>
         <v>42051.164031326349</v>
       </c>
       <c r="AH8" s="41"/>
@@ -7851,7 +7661,7 @@
         <v>9763.9014687261079</v>
       </c>
       <c r="H9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 AMS'!$N$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 AMS'!$N$12*20</f>
         <v>9712.4238402956325</v>
       </c>
       <c r="I9" s="69">
@@ -7871,7 +7681,7 @@
         <v>8879.5566916750031</v>
       </c>
       <c r="M9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 AMS'!S$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 AMS'!S$12*20</f>
         <v>8671.3399045198421</v>
       </c>
       <c r="N9" s="69">
@@ -7891,7 +7701,7 @@
         <v>10207.091641287898</v>
       </c>
       <c r="R9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 AMS'!X$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 AMS'!X$12*20</f>
         <v>10591.029575479908</v>
       </c>
       <c r="S9" s="69">
@@ -7911,7 +7721,7 @@
         <v>12837.249840028875</v>
       </c>
       <c r="W9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 AMS'!AC$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 AMS'!AC$12*20</f>
         <v>13398.804906166113</v>
       </c>
       <c r="X9" s="69">
@@ -7931,7 +7741,7 @@
         <v>13899.169906513895</v>
       </c>
       <c r="AB9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 AMS'!AH$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 AMS'!AH$12*20</f>
         <v>14024.26115660084</v>
       </c>
       <c r="AC9" s="69">
@@ -7951,7 +7761,7 @@
         <v>14528.381710895823</v>
       </c>
       <c r="AG9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 AMS'!AM$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 AMS'!AM$12*20</f>
         <v>14654.411849469572</v>
       </c>
       <c r="AH9" s="41"/>
@@ -10413,21 +10223,21 @@
       <c r="A1" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="118">
+      <c r="B1" s="119">
         <v>2030</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118">
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119">
         <v>2050</v>
       </c>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -10446,10 +10256,10 @@
       <c r="F2" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="119" t="s">
+      <c r="G2" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="119"/>
+      <c r="H2" s="120"/>
       <c r="I2" s="23" t="s">
         <v>36</v>
       </c>
@@ -10482,10 +10292,10 @@
       <c r="F3" s="26">
         <v>30</v>
       </c>
-      <c r="G3" s="120" t="s">
+      <c r="G3" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="121"/>
+      <c r="H3" s="122"/>
       <c r="I3" s="25" t="s">
         <v>42</v>
       </c>
@@ -10518,10 +10328,10 @@
       <c r="F4" s="26">
         <v>10</v>
       </c>
-      <c r="G4" s="116">
+      <c r="G4" s="117">
         <v>20</v>
       </c>
-      <c r="H4" s="117"/>
+      <c r="H4" s="118"/>
       <c r="I4" s="25">
         <v>20</v>
       </c>
@@ -10554,10 +10364,10 @@
       <c r="F5" s="26">
         <v>2</v>
       </c>
-      <c r="G5" s="116">
+      <c r="G5" s="117">
         <v>35</v>
       </c>
-      <c r="H5" s="117"/>
+      <c r="H5" s="118"/>
       <c r="I5" s="25">
         <v>5</v>
       </c>
@@ -10590,10 +10400,10 @@
       <c r="F6" s="26">
         <v>35</v>
       </c>
-      <c r="G6" s="116">
+      <c r="G6" s="117">
         <v>55</v>
       </c>
-      <c r="H6" s="117"/>
+      <c r="H6" s="118"/>
       <c r="I6" s="25">
         <v>55</v>
       </c>
@@ -10626,10 +10436,10 @@
       <c r="F7" s="26">
         <v>7</v>
       </c>
-      <c r="G7" s="116">
+      <c r="G7" s="117">
         <v>9</v>
       </c>
-      <c r="H7" s="117"/>
+      <c r="H7" s="118"/>
       <c r="I7" s="25">
         <v>20</v>
       </c>
@@ -10662,10 +10472,10 @@
       <c r="F8" s="26">
         <v>1</v>
       </c>
-      <c r="G8" s="116">
+      <c r="G8" s="117">
         <v>5</v>
       </c>
-      <c r="H8" s="117"/>
+      <c r="H8" s="118"/>
       <c r="I8" s="25">
         <v>5</v>
       </c>
@@ -10767,14 +10577,14 @@
       <c r="A17" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="122" t="s">
+      <c r="B17" s="116" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122" t="s">
+      <c r="C17" s="116"/>
+      <c r="D17" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="122"/>
+      <c r="E17" s="116"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
@@ -10831,10 +10641,10 @@
       <c r="A21" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="122">
+      <c r="B21" s="116">
         <v>300</v>
       </c>
-      <c r="C21" s="122">
+      <c r="C21" s="116">
         <v>300</v>
       </c>
       <c r="D21" s="49">
@@ -10848,8 +10658,8 @@
       <c r="A22" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="122"/>
-      <c r="C22" s="122"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="49">
         <v>2</v>
       </c>
@@ -10878,10 +10688,10 @@
       <c r="A24" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="122">
+      <c r="B24" s="116">
         <v>30</v>
       </c>
-      <c r="C24" s="122">
+      <c r="C24" s="116">
         <v>75</v>
       </c>
       <c r="D24" s="49">
@@ -10895,8 +10705,8 @@
       <c r="A25" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="122"/>
-      <c r="C25" s="122"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="116"/>
       <c r="D25" s="49">
         <v>10</v>
       </c>
@@ -10925,10 +10735,10 @@
       <c r="A27" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="122">
+      <c r="B27" s="116">
         <v>20</v>
       </c>
-      <c r="C27" s="122">
+      <c r="C27" s="116">
         <v>35</v>
       </c>
       <c r="D27" s="49">
@@ -10942,8 +10752,8 @@
       <c r="A28" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="122"/>
-      <c r="C28" s="122"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="116"/>
       <c r="D28" s="49">
         <v>1</v>
       </c>
@@ -11000,14 +10810,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
@@ -11017,6 +10819,14 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11063,7 +10873,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="114" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -11098,7 +10908,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="109"/>
+      <c r="A3" s="115"/>
       <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
@@ -11131,7 +10941,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="109"/>
+      <c r="A4" s="115"/>
       <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
@@ -11569,7 +11379,7 @@
       <c r="K17" s="9"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="108" t="s">
+      <c r="A18" s="114" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -11604,7 +11414,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="109"/>
+      <c r="A19" s="115"/>
       <c r="B19" s="6" t="s">
         <v>2</v>
       </c>
@@ -11637,7 +11447,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="109"/>
+      <c r="A20" s="115"/>
       <c r="B20" s="6" t="s">
         <v>3</v>
       </c>
@@ -12164,7 +11974,7 @@
       <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="114" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -12199,7 +12009,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="109"/>
+      <c r="A37" s="115"/>
       <c r="B37" s="6" t="s">
         <v>2</v>
       </c>
@@ -12232,7 +12042,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="109"/>
+      <c r="A38" s="115"/>
       <c r="B38" s="6" t="s">
         <v>3</v>
       </c>
@@ -12626,7 +12436,7 @@
       <c r="K49" s="9"/>
     </row>
     <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="108" t="s">
+      <c r="A50" s="114" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -12661,7 +12471,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="109"/>
+      <c r="A51" s="115"/>
       <c r="B51" s="6" t="s">
         <v>2</v>
       </c>
@@ -12694,7 +12504,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="109"/>
+      <c r="A52" s="115"/>
       <c r="B52" s="12" t="s">
         <v>3</v>
       </c>
@@ -12851,7 +12661,7 @@
       <c r="K56" s="9"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="108" t="s">
+      <c r="A57" s="114" t="s">
         <v>23</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -12888,7 +12698,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="109" t="s">
+      <c r="A58" s="115" t="s">
         <v>15</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -12925,7 +12735,7 @@
       </c>
     </row>
     <row r="59" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="109"/>
+      <c r="A59" s="115"/>
       <c r="B59" s="12" t="s">
         <v>18</v>
       </c>
@@ -12960,7 +12770,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="109"/>
+      <c r="A60" s="115"/>
       <c r="B60" s="6" t="s">
         <v>19</v>
       </c>
@@ -12995,7 +12805,7 @@
       </c>
     </row>
     <row r="61" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="109"/>
+      <c r="A61" s="115"/>
       <c r="B61" s="6" t="s">
         <v>21</v>
       </c>
@@ -13162,7 +12972,7 @@
       <c r="K65" s="9"/>
     </row>
     <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="108" t="s">
+      <c r="A66" s="114" t="s">
         <v>25</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -13199,7 +13009,7 @@
       </c>
     </row>
     <row r="67" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="109" t="s">
+      <c r="A67" s="115" t="s">
         <v>15</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -13236,7 +13046,7 @@
       </c>
     </row>
     <row r="68" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="109"/>
+      <c r="A68" s="115"/>
       <c r="B68" s="12" t="s">
         <v>18</v>
       </c>
@@ -13271,7 +13081,7 @@
       </c>
     </row>
     <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="109"/>
+      <c r="A69" s="115"/>
       <c r="B69" s="6" t="s">
         <v>19</v>
       </c>
@@ -13306,7 +13116,7 @@
       </c>
     </row>
     <row r="70" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="109"/>
+      <c r="A70" s="115"/>
       <c r="B70" s="6" t="s">
         <v>21</v>
       </c>
@@ -13638,31 +13448,31 @@
         <v>50</v>
       </c>
       <c r="C80" s="81">
-        <f>'[3]Cibles ThreeME v2 '!$I$7</f>
+        <f>'[6]Cibles ThreeME v2 '!$I$7</f>
         <v>24.904679182551273</v>
       </c>
       <c r="D80" s="81">
-        <f>'[3]Cibles ThreeME v2 '!$N$7</f>
+        <f>'[6]Cibles ThreeME v2 '!$N$7</f>
         <v>7.6163243247728092</v>
       </c>
       <c r="E80" s="84">
-        <f>'[3]Cibles ThreeME v2 '!$S$7</f>
+        <f>'[6]Cibles ThreeME v2 '!$S$7</f>
         <v>7.5523881054869557</v>
       </c>
       <c r="F80" s="81">
-        <f>'[3]Cibles ThreeME v2 '!$X$7</f>
+        <f>'[6]Cibles ThreeME v2 '!$X$7</f>
         <v>7.9623342705743987</v>
       </c>
       <c r="G80" s="81">
-        <f>'[3]Cibles ThreeME v2 '!$AC$7</f>
+        <f>'[6]Cibles ThreeME v2 '!$AC$7</f>
         <v>8.315170606453826</v>
       </c>
       <c r="H80" s="81">
-        <f>'[3]Cibles ThreeME v2 '!$AH$7</f>
+        <f>'[6]Cibles ThreeME v2 '!$AH$7</f>
         <v>8.579895509379492</v>
       </c>
       <c r="I80" s="81">
-        <f>'[3]Cibles ThreeME v2 '!$AM$7</f>
+        <f>'[6]Cibles ThreeME v2 '!$AM$7</f>
         <v>24.603178920457438</v>
       </c>
       <c r="J80" s="8"/>
@@ -15058,14 +14868,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A139:A142"/>
-    <mergeCell ref="A147:A150"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="A107:A110"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A131:A134"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A9:A11"/>
@@ -15078,6 +14880,14 @@
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A139:A142"/>
+    <mergeCell ref="A147:A150"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A131:A134"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A9" location="_ftn1" display="_ftn1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -15132,7 +14942,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="114" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -15172,7 +14982,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="109"/>
+      <c r="A3" s="115"/>
       <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
@@ -15210,7 +15020,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="109"/>
+      <c r="A4" s="115"/>
       <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
@@ -15297,27 +15107,27 @@
         <v>5.3111395326823425</v>
       </c>
       <c r="D6" s="51">
-        <f>[4]Production!D$36</f>
+        <f>[3]Production!D$36</f>
         <v>7.7070464641111505</v>
       </c>
       <c r="E6" s="51">
-        <f>[4]Production!E$36</f>
+        <f>[3]Production!E$36</f>
         <v>10.588971068279136</v>
       </c>
       <c r="F6" s="51">
-        <f>[4]Production!F$36</f>
+        <f>[3]Production!F$36</f>
         <v>14.458420531052537</v>
       </c>
       <c r="G6" s="51">
-        <f>[4]Production!G$36</f>
+        <f>[3]Production!G$36</f>
         <v>18.169659056823228</v>
       </c>
       <c r="H6" s="51">
-        <f>[4]Production!H$36</f>
+        <f>[3]Production!H$36</f>
         <v>21.574373255325391</v>
       </c>
       <c r="I6" s="51">
-        <f>[4]Production!I$36</f>
+        <f>[3]Production!I$36</f>
         <v>27.498580147533193</v>
       </c>
       <c r="J6" s="8"/>
@@ -15573,27 +15383,27 @@
         <v>2.0172086556820736</v>
       </c>
       <c r="D13" s="52">
-        <f>[4]Production!D$37</f>
+        <f>[3]Production!D$37</f>
         <v>2.2723765579551198</v>
       </c>
       <c r="E13" s="52">
-        <f>[4]Production!E$37</f>
+        <f>[3]Production!E$37</f>
         <v>2.4429006060973779</v>
       </c>
       <c r="F13" s="52">
-        <f>[4]Production!F$37</f>
+        <f>[3]Production!F$37</f>
         <v>3.5140427848919749</v>
       </c>
       <c r="G13" s="52">
-        <f>[4]Production!G$37</f>
+        <f>[3]Production!G$37</f>
         <v>4.5019986055673176</v>
       </c>
       <c r="H13" s="52">
-        <f>[4]Production!H$37</f>
+        <f>[3]Production!H$37</f>
         <v>5.4899543003083568</v>
       </c>
       <c r="I13" s="52">
-        <f>[4]Production!I$37</f>
+        <f>[3]Production!I$37</f>
         <v>6.4779101562551027</v>
       </c>
       <c r="J13" s="8"/>
@@ -15766,7 +15576,7 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="108" t="s">
+      <c r="A18" s="114" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -15806,7 +15616,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="109"/>
+      <c r="A19" s="115"/>
       <c r="B19" s="6" t="s">
         <v>2</v>
       </c>
@@ -15844,7 +15654,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="109"/>
+      <c r="A20" s="115"/>
       <c r="B20" s="6" t="s">
         <v>3</v>
       </c>
@@ -16203,27 +16013,27 @@
         <v>0</v>
       </c>
       <c r="D29" s="52">
-        <f>[4]Production!D$34</f>
+        <f>[3]Production!D$34</f>
         <v>2.6990746055000001E-11</v>
       </c>
       <c r="E29" s="52">
-        <f>[4]Production!E$34</f>
+        <f>[3]Production!E$34</f>
         <v>3.6527991733000001E-10</v>
       </c>
       <c r="F29" s="52">
-        <f>[4]Production!F$34</f>
+        <f>[3]Production!F$34</f>
         <v>9.0446673339799984E-10</v>
       </c>
       <c r="G29" s="52">
-        <f>[4]Production!G$34</f>
+        <f>[3]Production!G$34</f>
         <v>1.3689268202970003E-9</v>
       </c>
       <c r="H29" s="52">
-        <f>[4]Production!H$34</f>
+        <f>[3]Production!H$34</f>
         <v>1.1570629432770425</v>
       </c>
       <c r="I29" s="52">
-        <f>[4]Production!I$34</f>
+        <f>[3]Production!I$34</f>
         <v>44.834316178932511</v>
       </c>
       <c r="J29" s="8"/>
@@ -16319,27 +16129,27 @@
         <v>3.9812948257280469</v>
       </c>
       <c r="D32" s="51">
-        <f>[4]Investissements!D$9</f>
+        <f>[3]Investissements!D$9</f>
         <v>15.600000000003027</v>
       </c>
       <c r="E32" s="51">
-        <f>[4]Investissements!E$9</f>
+        <f>[3]Investissements!E$9</f>
         <v>20.000000000018925</v>
       </c>
       <c r="F32" s="51">
-        <f>[4]Investissements!F$9</f>
+        <f>[3]Investissements!F$9</f>
         <v>28.750000000480206</v>
       </c>
       <c r="G32" s="51">
-        <f>[4]Investissements!G$9</f>
+        <f>[3]Investissements!G$9</f>
         <v>37.500000002109303</v>
       </c>
       <c r="H32" s="51">
-        <f>[4]Investissements!H$9</f>
+        <f>[3]Investissements!H$9</f>
         <v>46.250000001496062</v>
       </c>
       <c r="I32" s="51">
-        <f>[4]Investissements!I$9</f>
+        <f>[3]Investissements!I$9</f>
         <v>66.000000000018645</v>
       </c>
       <c r="J32" s="8"/>
@@ -16472,7 +16282,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="114" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -16512,7 +16322,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="109"/>
+      <c r="A37" s="115"/>
       <c r="B37" s="6" t="s">
         <v>2</v>
       </c>
@@ -16550,7 +16360,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="109"/>
+      <c r="A38" s="115"/>
       <c r="B38" s="6" t="s">
         <v>3</v>
       </c>
@@ -16641,23 +16451,23 @@
         <v>50.772959999999998</v>
       </c>
       <c r="E40" s="51">
-        <f>[4]Production!E$39</f>
+        <f>[3]Production!E$39</f>
         <v>70.355046444793672</v>
       </c>
       <c r="F40" s="51">
-        <f>[4]Production!F$39</f>
+        <f>[3]Production!F$39</f>
         <v>92.759339784844244</v>
       </c>
       <c r="G40" s="51">
-        <f>[4]Production!G$39</f>
+        <f>[3]Production!G$39</f>
         <v>115.11804204176454</v>
       </c>
       <c r="H40" s="51">
-        <f>[4]Production!H$39</f>
+        <f>[3]Production!H$39</f>
         <v>141.51337418169942</v>
       </c>
       <c r="I40" s="51">
-        <f>[4]Production!I$39</f>
+        <f>[3]Production!I$39</f>
         <v>175.11117102622472</v>
       </c>
       <c r="J40" s="8"/>
@@ -17021,7 +16831,7 @@
       <c r="L49" s="82"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="108" t="s">
+      <c r="A50" s="114" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -17061,7 +16871,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="109"/>
+      <c r="A51" s="115"/>
       <c r="B51" s="6" t="s">
         <v>2</v>
       </c>
@@ -17099,7 +16909,7 @@
       </c>
     </row>
     <row r="52" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="109"/>
+      <c r="A52" s="115"/>
       <c r="B52" s="12" t="s">
         <v>3</v>
       </c>
@@ -17291,7 +17101,7 @@
       <c r="L56" s="82"/>
     </row>
     <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="108" t="s">
+      <c r="A57" s="114" t="s">
         <v>23</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -17339,7 +17149,7 @@
       </c>
     </row>
     <row r="58" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="109" t="s">
+      <c r="A58" s="115" t="s">
         <v>15</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -17387,7 +17197,7 @@
       </c>
     </row>
     <row r="59" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="109"/>
+      <c r="A59" s="115"/>
       <c r="B59" s="12" t="s">
         <v>18</v>
       </c>
@@ -17433,7 +17243,7 @@
       </c>
     </row>
     <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="109"/>
+      <c r="A60" s="115"/>
       <c r="B60" s="6" t="s">
         <v>19</v>
       </c>
@@ -17476,7 +17286,7 @@
       <c r="L60" s="82"/>
     </row>
     <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="109"/>
+      <c r="A61" s="115"/>
       <c r="B61" s="6" t="s">
         <v>21</v>
       </c>
@@ -17688,7 +17498,7 @@
       </c>
     </row>
     <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="108" t="s">
+      <c r="A66" s="114" t="s">
         <v>25</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -17736,7 +17546,7 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="109" t="s">
+      <c r="A67" s="115" t="s">
         <v>15</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -17784,7 +17594,7 @@
       </c>
     </row>
     <row r="68" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="109"/>
+      <c r="A68" s="115"/>
       <c r="B68" s="12" t="s">
         <v>18</v>
       </c>
@@ -17830,7 +17640,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="109"/>
+      <c r="A69" s="115"/>
       <c r="B69" s="6" t="s">
         <v>19</v>
       </c>
@@ -17873,7 +17683,7 @@
       <c r="L69" s="82"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="109"/>
+      <c r="A70" s="115"/>
       <c r="B70" s="6" t="s">
         <v>21</v>
       </c>
@@ -17998,11 +17808,11 @@
         <v>97.61866770412874</v>
       </c>
       <c r="J72" s="51">
-        <f>[4]Production!J$172</f>
+        <f>[3]Production!J$172</f>
         <v>0</v>
       </c>
       <c r="K72" s="51">
-        <f>[4]Production!K$172</f>
+        <f>[3]Production!K$172</f>
         <v>0</v>
       </c>
       <c r="L72" s="83">
@@ -18254,7 +18064,7 @@
         <v>6.1640014823452782</v>
       </c>
       <c r="D79" s="51">
-        <f>[4]Investissements!D$5</f>
+        <f>[3]Investissements!D$5</f>
         <v>6.1640005659265498</v>
       </c>
       <c r="E79" s="53">
@@ -18289,27 +18099,27 @@
         <v>24.904679182551273</v>
       </c>
       <c r="D80" s="52">
-        <f>'[3]Cibles ThreeME v2 AMS'!$N$7</f>
+        <f>'[6]Cibles ThreeME v2 AMS'!$N$7</f>
         <v>26.434633696901958</v>
       </c>
       <c r="E80" s="52">
-        <f>'[3]Cibles ThreeME v2 AMS'!$S$7</f>
+        <f>'[6]Cibles ThreeME v2 AMS'!$S$7</f>
         <v>23.012014275261006</v>
       </c>
       <c r="F80" s="52">
-        <f>'[3]Cibles ThreeME v2 AMS'!$X$7</f>
+        <f>'[6]Cibles ThreeME v2 AMS'!$X$7</f>
         <v>17.076239626292423</v>
       </c>
       <c r="G80" s="52">
-        <f>'[3]Cibles ThreeME v2 AMS'!$AC$7</f>
+        <f>'[6]Cibles ThreeME v2 AMS'!$AC$7</f>
         <v>1.9497760583305019</v>
       </c>
       <c r="H80" s="52">
-        <f>'[3]Cibles ThreeME v2 AMS'!$AH$7</f>
+        <f>'[6]Cibles ThreeME v2 AMS'!$AH$7</f>
         <v>2.6500221012566496</v>
       </c>
       <c r="I80" s="52">
-        <f>'[3]Cibles ThreeME v2 AMS'!$AM$7</f>
+        <f>'[6]Cibles ThreeME v2 AMS'!$AM$7</f>
         <v>3.1772529313232827</v>
       </c>
       <c r="J80" s="8"/>
@@ -18563,35 +18373,35 @@
         <v>221.51940118075376</v>
       </c>
       <c r="D87" s="52">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="E87" s="52">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="F87" s="52">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="G87" s="52">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="H87" s="52">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="I87" s="52">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="J87" s="8">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="K87" s="8">
-        <f>[4]Investissements!$C$6</f>
+        <f>[3]Investissements!$C$6</f>
         <v>1.8500001452782728</v>
       </c>
       <c r="L87" s="82">
@@ -18609,27 +18419,27 @@
         <v>221.51940118075376</v>
       </c>
       <c r="D88" s="52">
-        <f>[4]Production!D$6</f>
+        <f>[3]Production!D$6</f>
         <v>4.9720475149880108E-3</v>
       </c>
       <c r="E88" s="52">
-        <f>[4]Production!E$6</f>
+        <f>[3]Production!E$6</f>
         <v>1.2858088192232258E-2</v>
       </c>
       <c r="F88" s="52">
-        <f>[4]Production!F$6</f>
+        <f>[3]Production!F$6</f>
         <v>1.5238144340667708E-2</v>
       </c>
       <c r="G88" s="52">
-        <f>[4]Production!G$6</f>
+        <f>[3]Production!G$6</f>
         <v>1.2088206144485428E-2</v>
       </c>
       <c r="H88" s="52">
-        <f>[4]Production!H$6</f>
+        <f>[3]Production!H$6</f>
         <v>3.6956358810318495E-2</v>
       </c>
       <c r="I88" s="52">
-        <f>[4]Production!I$6</f>
+        <f>[3]Production!I$6</f>
         <v>5.1156976572074533E-2</v>
       </c>
       <c r="J88" s="8"/>
@@ -18803,39 +18613,39 @@
         <v>47</v>
       </c>
       <c r="C95" s="8">
-        <f>[4]Investissements!C$15</f>
+        <f>[3]Investissements!C$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="D95" s="8">
-        <f>[4]Investissements!D$15</f>
+        <f>[3]Investissements!D$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="E95" s="8">
-        <f>[4]Investissements!E$15</f>
+        <f>[3]Investissements!E$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="F95" s="8">
-        <f>[4]Investissements!F$15</f>
+        <f>[3]Investissements!F$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="G95" s="8">
-        <f>[4]Investissements!G$15</f>
+        <f>[3]Investissements!G$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="H95" s="8">
-        <f>[4]Investissements!H$15</f>
+        <f>[3]Investissements!H$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="I95" s="8">
-        <f>[4]Investissements!I$15</f>
+        <f>[3]Investissements!I$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="J95" s="8">
-        <f>[4]Investissements!J$15</f>
+        <f>[3]Investissements!J$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="K95" s="8">
-        <f>[4]Investissements!K$15</f>
+        <f>[3]Investissements!K$15</f>
         <v>0.48361560000000559</v>
       </c>
       <c r="L95" s="82">
@@ -18849,31 +18659,31 @@
         <v>50</v>
       </c>
       <c r="C96" s="8">
-        <f>[4]Production!C$15</f>
+        <f>[3]Production!C$15</f>
         <v>2.3799584888399989</v>
       </c>
       <c r="D96" s="8">
-        <f>[4]Production!D$15</f>
+        <f>[3]Production!D$15</f>
         <v>2.3799584888399989</v>
       </c>
       <c r="E96" s="8">
-        <f>[4]Production!E$15</f>
+        <f>[3]Production!E$15</f>
         <v>2.3799584888399989</v>
       </c>
       <c r="F96" s="8">
-        <f>[4]Production!F$15</f>
+        <f>[3]Production!F$15</f>
         <v>2.3799584888399989</v>
       </c>
       <c r="G96" s="8">
-        <f>[4]Production!G$15</f>
+        <f>[3]Production!G$15</f>
         <v>2.3799584888399989</v>
       </c>
       <c r="H96" s="8">
-        <f>[4]Production!H$15</f>
+        <f>[3]Production!H$15</f>
         <v>2.3799584888399989</v>
       </c>
       <c r="I96" s="8">
-        <f>[4]Production!I$15</f>
+        <f>[3]Production!I$15</f>
         <v>2.3799584888399989</v>
       </c>
       <c r="J96" s="8"/>
@@ -19005,31 +18815,31 @@
         <v>47</v>
       </c>
       <c r="C103" s="8">
-        <f>[4]Investissements!C$16</f>
+        <f>[3]Investissements!C$16</f>
         <v>0.65390400000002646</v>
       </c>
       <c r="D103" s="8">
-        <f>[4]Investissements!D$16</f>
+        <f>[3]Investissements!D$16</f>
         <v>0.80000000000005866</v>
       </c>
       <c r="E103" s="8">
-        <f>[4]Investissements!E$16</f>
+        <f>[3]Investissements!E$16</f>
         <v>0.80000000000005866</v>
       </c>
       <c r="F103" s="8">
-        <f>[4]Investissements!F$16</f>
+        <f>[3]Investissements!F$16</f>
         <v>0.80000000000005866</v>
       </c>
       <c r="G103" s="8">
-        <f>[4]Investissements!G$16</f>
+        <f>[3]Investissements!G$16</f>
         <v>0.80000000000005866</v>
       </c>
       <c r="H103" s="8">
-        <f>[4]Investissements!H$16</f>
+        <f>[3]Investissements!H$16</f>
         <v>0.80000000000005866</v>
       </c>
       <c r="I103" s="8">
-        <f>[4]Investissements!I$16</f>
+        <f>[3]Investissements!I$16</f>
         <v>0.80000000000005866</v>
       </c>
       <c r="J103" s="8"/>
@@ -19045,31 +18855,31 @@
         <v>50</v>
       </c>
       <c r="C104" s="8">
-        <f>[4]Production!C$16</f>
+        <f>[3]Production!C$16</f>
         <v>1.6037893462559989</v>
       </c>
       <c r="D104" s="8">
-        <f>[4]Production!D$16</f>
+        <f>[3]Production!D$16</f>
         <v>1.9621097277623976</v>
       </c>
       <c r="E104" s="8">
-        <f>[4]Production!E$16</f>
+        <f>[3]Production!E$16</f>
         <v>1.9621097277623976</v>
       </c>
       <c r="F104" s="8">
-        <f>[4]Production!F$16</f>
+        <f>[3]Production!F$16</f>
         <v>1.9621097277623976</v>
       </c>
       <c r="G104" s="8">
-        <f>[4]Production!G$16</f>
+        <f>[3]Production!G$16</f>
         <v>1.9621097277623976</v>
       </c>
       <c r="H104" s="8">
-        <f>[4]Production!H$16</f>
+        <f>[3]Production!H$16</f>
         <v>1.9621097277623976</v>
       </c>
       <c r="I104" s="8">
-        <f>[4]Production!I$16</f>
+        <f>[3]Production!I$16</f>
         <v>1.9621097277623976</v>
       </c>
       <c r="J104" s="8"/>
@@ -19201,31 +19011,31 @@
         <v>47</v>
       </c>
       <c r="C111" s="8">
-        <f>[4]Investissements!C$14</f>
+        <f>[3]Investissements!C$14</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="D111" s="8">
-        <f>[4]Investissements!D$14</f>
+        <f>[3]Investissements!D$14</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="E111" s="8">
-        <f>[4]Investissements!E$14</f>
+        <f>[3]Investissements!E$14</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="F111" s="8">
-        <f>[4]Investissements!F$14</f>
+        <f>[3]Investissements!F$14</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="G111" s="8">
-        <f>[4]Investissements!G$14</f>
+        <f>[3]Investissements!G$14</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="H111" s="8">
-        <f>[4]Investissements!H$14</f>
+        <f>[3]Investissements!H$14</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="I111" s="8">
-        <f>[4]Investissements!I$14</f>
+        <f>[3]Investissements!I$14</f>
         <v>0.24000000000000002</v>
       </c>
       <c r="J111" s="8"/>
@@ -19241,31 +19051,31 @@
         <v>50</v>
       </c>
       <c r="C112" s="8">
-        <f>[4]Production!C$14</f>
+        <f>[3]Production!C$14</f>
         <v>0.46126655999999999</v>
       </c>
       <c r="D112" s="8">
-        <f>[4]Production!D$14</f>
+        <f>[3]Production!D$14</f>
         <v>0.46126655999999999</v>
       </c>
       <c r="E112" s="8">
-        <f>[4]Production!E$14</f>
+        <f>[3]Production!E$14</f>
         <v>0.46126655999999999</v>
       </c>
       <c r="F112" s="8">
-        <f>[4]Production!F$14</f>
+        <f>[3]Production!F$14</f>
         <v>0.46126655999999999</v>
       </c>
       <c r="G112" s="8">
-        <f>[4]Production!G$14</f>
+        <f>[3]Production!G$14</f>
         <v>0.46126655999999999</v>
       </c>
       <c r="H112" s="8">
-        <f>[4]Production!H$14</f>
+        <f>[3]Production!H$14</f>
         <v>0.46126655999999999</v>
       </c>
       <c r="I112" s="8">
-        <f>[4]Production!I$14</f>
+        <f>[3]Production!I$14</f>
         <v>0.46126655999999999</v>
       </c>
       <c r="J112" s="8"/>
@@ -19397,31 +19207,31 @@
         <v>47</v>
       </c>
       <c r="C119" s="8">
-        <f>[4]Investissements!$C$18</f>
+        <f>[3]Investissements!$C$18</f>
         <v>1.8500000000002501E-3</v>
       </c>
       <c r="D119" s="8">
-        <f>[4]Investissements!$C$18</f>
+        <f>[3]Investissements!$C$18</f>
         <v>1.8500000000002501E-3</v>
       </c>
       <c r="E119" s="8">
-        <f>[4]Investissements!$C$18</f>
+        <f>[3]Investissements!$C$18</f>
         <v>1.8500000000002501E-3</v>
       </c>
       <c r="F119" s="8">
-        <f>[4]Investissements!$C$18</f>
+        <f>[3]Investissements!$C$18</f>
         <v>1.8500000000002501E-3</v>
       </c>
       <c r="G119" s="8">
-        <f>[4]Investissements!$C$18</f>
+        <f>[3]Investissements!$C$18</f>
         <v>1.8500000000002501E-3</v>
       </c>
       <c r="H119" s="8">
-        <f>[4]Investissements!$C$18</f>
+        <f>[3]Investissements!$C$18</f>
         <v>1.8500000000002501E-3</v>
       </c>
       <c r="I119" s="8">
-        <f>[4]Investissements!$C$18</f>
+        <f>[3]Investissements!$C$18</f>
         <v>1.8500000000002501E-3</v>
       </c>
       <c r="J119" s="8"/>
@@ -19437,31 +19247,31 @@
         <v>50</v>
       </c>
       <c r="C120" s="8">
-        <f>[4]Production!C$18</f>
+        <f>[3]Production!C$18</f>
         <v>4.69974E-3</v>
       </c>
       <c r="D120" s="8">
-        <f>[4]Production!D$18</f>
+        <f>[3]Production!D$18</f>
         <v>6.0969599999999999E-2</v>
       </c>
       <c r="E120" s="8">
-        <f>[4]Production!E$18</f>
+        <f>[3]Production!E$18</f>
         <v>6.0969599999999999E-2</v>
       </c>
       <c r="F120" s="8">
-        <f>[4]Production!F$18</f>
+        <f>[3]Production!F$18</f>
         <v>6.0969599999999999E-2</v>
       </c>
       <c r="G120" s="8">
-        <f>[4]Production!G$18</f>
+        <f>[3]Production!G$18</f>
         <v>6.0969599999999999E-2</v>
       </c>
       <c r="H120" s="8">
-        <f>[4]Production!H$18</f>
+        <f>[3]Production!H$18</f>
         <v>6.0969599999999999E-2</v>
       </c>
       <c r="I120" s="8">
-        <f>[4]Production!I$18</f>
+        <f>[3]Production!I$18</f>
         <v>6.0969599999999999E-2</v>
       </c>
       <c r="J120" s="8"/>
@@ -19593,39 +19403,39 @@
         <v>47</v>
       </c>
       <c r="C127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!C$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!C$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="D127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!D$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!D$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="E127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!E$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!E$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="F127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!F$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!F$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="G127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!G$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!G$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="H127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!H$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!H$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="I127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!I$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!I$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="J127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!J$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!J$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="K127" s="8">
-        <f>[4]Investissements!$C$19+[4]Investissements!K$21</f>
+        <f>[3]Investissements!$C$19+[3]Investissements!K$21</f>
         <v>30.473000000000003</v>
       </c>
       <c r="L127" s="82">
@@ -19639,31 +19449,31 @@
         <v>50</v>
       </c>
       <c r="C128" s="51">
-        <f>[4]Production!C$19+[4]Production!C$23</f>
+        <f>[3]Production!C$19+[3]Production!C$23</f>
         <v>66.59069938102958</v>
       </c>
       <c r="D128" s="51">
-        <f>[4]Production!D$19+[4]Production!D$23</f>
+        <f>[3]Production!D$19+[3]Production!D$23</f>
         <v>67.382236739646132</v>
       </c>
       <c r="E128" s="51">
-        <f>[4]Production!E$19+[4]Production!E$23</f>
+        <f>[3]Production!E$19+[3]Production!E$23</f>
         <v>69.352691340375216</v>
       </c>
       <c r="F128" s="51">
-        <f>[4]Production!F$19+[4]Production!F$23</f>
+        <f>[3]Production!F$19+[3]Production!F$23</f>
         <v>69.354776815807597</v>
       </c>
       <c r="G128" s="51">
-        <f>[4]Production!G$19+[4]Production!G$23</f>
+        <f>[3]Production!G$19+[3]Production!G$23</f>
         <v>70.042780399166446</v>
       </c>
       <c r="H128" s="51">
-        <f>[4]Production!H$19+[4]Production!H$23</f>
+        <f>[3]Production!H$19+[3]Production!H$23</f>
         <v>70.271845903081896</v>
       </c>
       <c r="I128" s="51">
-        <f>[4]Production!I$19+[4]Production!I$23</f>
+        <f>[3]Production!I$19+[3]Production!I$23</f>
         <v>70.085273385543928</v>
       </c>
       <c r="J128" s="8"/>
@@ -19795,31 +19605,31 @@
         <v>47</v>
       </c>
       <c r="C135" s="52">
-        <f>[4]Investissements!C$20</f>
+        <f>[3]Investissements!C$20</f>
         <v>4.11224892653E-7</v>
       </c>
       <c r="D135" s="52">
-        <f>[4]Investissements!D$20</f>
+        <f>[3]Investissements!D$20</f>
         <v>8.1130696045799994E-7</v>
       </c>
       <c r="E135" s="52">
-        <f>[4]Investissements!E$20</f>
+        <f>[3]Investissements!E$20</f>
         <v>1.4413728045000003E-6</v>
       </c>
       <c r="F135" s="52">
-        <f>[4]Investissements!F$20</f>
+        <f>[3]Investissements!F$20</f>
         <v>0.21040230769474819</v>
       </c>
       <c r="G135" s="52">
-        <f>[4]Investissements!G$20</f>
+        <f>[3]Investissements!G$20</f>
         <v>0.21040235354440281</v>
       </c>
       <c r="H135" s="52">
-        <f>[4]Investissements!H$20</f>
+        <f>[3]Investissements!H$20</f>
         <v>0.21040196962776603</v>
       </c>
       <c r="I135" s="52">
-        <f>[4]Investissements!I$20</f>
+        <f>[3]Investissements!I$20</f>
         <v>0.21040135790046022</v>
       </c>
       <c r="J135" s="8"/>
@@ -19835,31 +19645,31 @@
         <v>50</v>
       </c>
       <c r="C136" s="51">
-        <f>[4]Production!C$24</f>
+        <f>[3]Production!C$24</f>
         <v>2.1252157036899895E-6</v>
       </c>
       <c r="D136" s="51">
-        <f>[4]Production!D$24</f>
+        <f>[3]Production!D$24</f>
         <v>3.9829152014953135E-6</v>
       </c>
       <c r="E136" s="51">
-        <f>[4]Production!E$24</f>
+        <f>[3]Production!E$24</f>
         <v>6.946818255577103E-6</v>
       </c>
       <c r="F136" s="51">
-        <f>[4]Production!F$24</f>
+        <f>[3]Production!F$24</f>
         <v>7.920989322727684E-2</v>
       </c>
       <c r="G136" s="51">
-        <f>[4]Production!G$24</f>
+        <f>[3]Production!G$24</f>
         <v>8.1284731822778192E-2</v>
       </c>
       <c r="H136" s="51">
-        <f>[4]Production!H$24</f>
+        <f>[3]Production!H$24</f>
         <v>8.7879215817297879E-2</v>
       </c>
       <c r="I136" s="51">
-        <f>[4]Production!I$24</f>
+        <f>[3]Production!I$24</f>
         <v>8.090124002506853E-2</v>
       </c>
       <c r="J136" s="8"/>
@@ -19991,31 +19801,31 @@
         <v>47</v>
       </c>
       <c r="C143" s="51">
-        <f>[4]Investissements!C$24+[4]Investissements!C$25</f>
+        <f>[3]Investissements!C$24+[3]Investissements!C$25</f>
         <v>0</v>
       </c>
       <c r="D143" s="51">
-        <f>[4]Investissements!D$24+[4]Investissements!D$25</f>
+        <f>[3]Investissements!D$24+[3]Investissements!D$25</f>
         <v>2.0603609844192055</v>
       </c>
       <c r="E143" s="51">
-        <f>[4]Investissements!E$24+[4]Investissements!E$25</f>
+        <f>[3]Investissements!E$24+[3]Investissements!E$25</f>
         <v>7.3145451013020617</v>
       </c>
       <c r="F143" s="51">
-        <f>[4]Investissements!F$24+[4]Investissements!F$25</f>
+        <f>[3]Investissements!F$24+[3]Investissements!F$25</f>
         <v>15.538877700726058</v>
       </c>
       <c r="G143" s="51">
-        <f>[4]Investissements!G$24+[4]Investissements!G$25</f>
+        <f>[3]Investissements!G$24+[3]Investissements!G$25</f>
         <v>22.848214332043106</v>
       </c>
       <c r="H143" s="51">
-        <f>[4]Investissements!H$24+[4]Investissements!H$25</f>
+        <f>[3]Investissements!H$24+[3]Investissements!H$25</f>
         <v>25.748732414052725</v>
       </c>
       <c r="I143" s="51">
-        <f>[4]Investissements!I$24+[4]Investissements!I$25</f>
+        <f>[3]Investissements!I$24+[3]Investissements!I$25</f>
         <v>40.211874328333536</v>
       </c>
       <c r="J143" s="8"/>
@@ -20031,31 +19841,31 @@
         <v>50</v>
       </c>
       <c r="C144" s="51">
-        <f>[4]Production!C$27+[4]Production!C$28</f>
+        <f>[3]Production!C$27+[3]Production!C$28</f>
         <v>0</v>
       </c>
       <c r="D144" s="51">
-        <f>[4]Production!D$27+[4]Production!D$28</f>
+        <f>[3]Production!D$27+[3]Production!D$28</f>
         <v>9.412070935361907</v>
       </c>
       <c r="E144" s="51">
-        <f>[4]Production!E$27+[4]Production!E$28</f>
+        <f>[3]Production!E$27+[3]Production!E$28</f>
         <v>26.432442142169513</v>
       </c>
       <c r="F144" s="51">
-        <f>[4]Production!F$27+[4]Production!F$28</f>
+        <f>[3]Production!F$27+[3]Production!F$28</f>
         <v>42.973872913816216</v>
       </c>
       <c r="G144" s="51">
-        <f>[4]Production!G$27+[4]Production!G$28</f>
+        <f>[3]Production!G$27+[3]Production!G$28</f>
         <v>58.580775432496679</v>
       </c>
       <c r="H144" s="51">
-        <f>[4]Production!H$27+[4]Production!H$28</f>
+        <f>[3]Production!H$27+[3]Production!H$28</f>
         <v>73.121543762940746</v>
       </c>
       <c r="I144" s="51">
-        <f>[4]Production!I$27+[4]Production!I$28</f>
+        <f>[3]Production!I$27+[3]Production!I$28</f>
         <v>103.17894775964206</v>
       </c>
       <c r="J144" s="8"/>
@@ -20187,31 +19997,31 @@
         <v>47</v>
       </c>
       <c r="C151" s="8">
-        <f>[4]Investissements!C$17</f>
+        <f>[3]Investissements!C$17</f>
         <v>0.87828299999994663</v>
       </c>
       <c r="D151" s="8">
-        <f>[4]Investissements!D$17</f>
+        <f>[3]Investissements!D$17</f>
         <v>0.87828299999994663</v>
       </c>
       <c r="E151" s="8">
-        <f>[4]Investissements!E$17</f>
+        <f>[3]Investissements!E$17</f>
         <v>0.87828299999994663</v>
       </c>
       <c r="F151" s="8">
-        <f>[4]Investissements!F$17</f>
+        <f>[3]Investissements!F$17</f>
         <v>0.87828299999994663</v>
       </c>
       <c r="G151" s="8">
-        <f>[4]Investissements!G$17</f>
+        <f>[3]Investissements!G$17</f>
         <v>0.87828299999994663</v>
       </c>
       <c r="H151" s="8">
-        <f>[4]Investissements!H$17</f>
+        <f>[3]Investissements!H$17</f>
         <v>0.87828299999994663</v>
       </c>
       <c r="I151" s="8">
-        <f>[4]Investissements!I$17</f>
+        <f>[3]Investissements!I$17</f>
         <v>0.87828299999994663</v>
       </c>
       <c r="J151" s="8"/>
@@ -20227,31 +20037,31 @@
         <v>50</v>
       </c>
       <c r="C152" s="8">
-        <f>[4]Production!C$17</f>
+        <f>[3]Production!C$17</f>
         <v>3.144046932672</v>
       </c>
       <c r="D152" s="8">
-        <f>[4]Production!D$17</f>
+        <f>[3]Production!D$17</f>
         <v>3.144046932672</v>
       </c>
       <c r="E152" s="8">
-        <f>[4]Production!E$17</f>
+        <f>[3]Production!E$17</f>
         <v>3.144046932672</v>
       </c>
       <c r="F152" s="8">
-        <f>[4]Production!F$17</f>
+        <f>[3]Production!F$17</f>
         <v>3.144046932672</v>
       </c>
       <c r="G152" s="8">
-        <f>[4]Production!G$17</f>
+        <f>[3]Production!G$17</f>
         <v>3.144046932672</v>
       </c>
       <c r="H152" s="8">
-        <f>[4]Production!H$17</f>
+        <f>[3]Production!H$17</f>
         <v>3.144046932672</v>
       </c>
       <c r="I152" s="8">
-        <f>[4]Production!I$17</f>
+        <f>[3]Production!I$17</f>
         <v>3.144046932672</v>
       </c>
       <c r="J152" s="8"/>
@@ -20399,14 +20209,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A123:A126"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A139:A142"/>
-    <mergeCell ref="A147:A150"/>
-    <mergeCell ref="A91:A94"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="A115:A118"/>
-    <mergeCell ref="A107:A110"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A9:A11"/>
@@ -20419,6 +20221,14 @@
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A123:A126"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A139:A142"/>
+    <mergeCell ref="A147:A150"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="A115:A118"/>
+    <mergeCell ref="A107:A110"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A9" location="_ftn1" display="_ftn1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -20479,7 +20289,7 @@
         <v>88</v>
       </c>
       <c r="B2" s="69">
-        <f>'[5]CU énergie'!$F48</f>
+        <f>'[4]CU énergie'!$F48</f>
         <v>18.979902880269496</v>
       </c>
       <c r="C2" s="69">
@@ -20516,11 +20326,11 @@
         <v>89</v>
       </c>
       <c r="B3" s="69">
-        <f>'[5]CU énergie'!$F49</f>
+        <f>'[4]CU énergie'!$F49</f>
         <v>122.57599999999999</v>
       </c>
       <c r="C3" s="69">
-        <f>'[5]CU énergie'!$F49</f>
+        <f>'[4]CU énergie'!$F49</f>
         <v>122.57599999999999</v>
       </c>
       <c r="D3" s="69">
@@ -20553,11 +20363,11 @@
         <v>90</v>
       </c>
       <c r="B4" s="69">
-        <f>'[5]CU énergie'!$F50</f>
+        <f>'[4]CU énergie'!$F50</f>
         <v>10.162299686291657</v>
       </c>
       <c r="C4" s="69">
-        <f>'[5]CU énergie'!$F50</f>
+        <f>'[4]CU énergie'!$F50</f>
         <v>10.162299686291657</v>
       </c>
       <c r="D4" s="69">
@@ -20590,11 +20400,11 @@
         <v>91</v>
       </c>
       <c r="B5" s="69">
-        <f>'[5]CU énergie'!$F51</f>
+        <f>'[4]CU énergie'!$F51</f>
         <v>14.31960410341097</v>
       </c>
       <c r="C5" s="69">
-        <f>'[5]CU énergie'!$F51</f>
+        <f>'[4]CU énergie'!$F51</f>
         <v>14.31960410341097</v>
       </c>
       <c r="D5" s="69">
@@ -20627,7 +20437,7 @@
         <v>92</v>
       </c>
       <c r="B6" s="69">
-        <f>'[5]CU énergie'!$F52</f>
+        <f>'[4]CU énergie'!$F52</f>
         <v>70.593025247882508</v>
       </c>
       <c r="C6" s="69">
@@ -20664,7 +20474,7 @@
         <v>93</v>
       </c>
       <c r="B7" s="69">
-        <f>'[5]CU énergie'!$F53</f>
+        <f>'[4]CU énergie'!$F53</f>
         <v>119.98755838887863</v>
       </c>
       <c r="C7" s="69">
@@ -20701,11 +20511,11 @@
         <v>94</v>
       </c>
       <c r="B8" s="69">
-        <f>'[5]CU énergie'!$F54</f>
+        <f>'[4]CU énergie'!$F54</f>
         <v>15</v>
       </c>
       <c r="C8" s="69">
-        <f>'[5]CU énergie'!$F54</f>
+        <f>'[4]CU énergie'!$F54</f>
         <v>15</v>
       </c>
       <c r="D8" s="69">
@@ -20738,11 +20548,11 @@
         <v>95</v>
       </c>
       <c r="B9" s="69">
-        <f>'[5]CU énergie'!$F55</f>
+        <f>'[4]CU énergie'!$F55</f>
         <v>61.9</v>
       </c>
       <c r="C9" s="69">
-        <f>'[5]CU énergie'!$F55</f>
+        <f>'[4]CU énergie'!$F55</f>
         <v>61.9</v>
       </c>
       <c r="D9" s="69">
@@ -21102,7 +20912,7 @@
         <v>88</v>
       </c>
       <c r="B2" s="69">
-        <f>'[5]CU énergie'!$H48</f>
+        <f>'[4]CU énergie'!$H48</f>
         <v>21.052878725363069</v>
       </c>
       <c r="C2" s="69">
@@ -21139,35 +20949,35 @@
         <v>89</v>
       </c>
       <c r="B3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="C3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="D3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="E3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="F3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="G3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="H3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="I3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
     </row>
@@ -21176,35 +20986,35 @@
         <v>90</v>
       </c>
       <c r="B4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="C4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="D4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="E4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="F4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="G4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="H4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="I4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
     </row>
@@ -21213,35 +21023,35 @@
         <v>91</v>
       </c>
       <c r="B5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="C5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="D5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="E5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="F5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="G5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="H5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="I5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
     </row>
@@ -21250,7 +21060,7 @@
         <v>92</v>
       </c>
       <c r="B6" s="69">
-        <f>'[5]CU énergie'!$H52</f>
+        <f>'[4]CU énergie'!$H52</f>
         <v>12.9338359643712</v>
       </c>
       <c r="C6" s="69">
@@ -21287,7 +21097,7 @@
         <v>93</v>
       </c>
       <c r="B7" s="69">
-        <f>'[5]CU énergie'!$H53</f>
+        <f>'[4]CU énergie'!$H53</f>
         <v>62.140352394535242</v>
       </c>
       <c r="C7" s="69">
@@ -21324,35 +21134,35 @@
         <v>94</v>
       </c>
       <c r="B8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="C8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="D8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="E8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="F8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="G8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="H8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="I8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
     </row>
@@ -21361,35 +21171,35 @@
         <v>95</v>
       </c>
       <c r="B9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="C9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="D9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="E9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="F9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="G9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="H9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="I9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
     </row>
@@ -21725,7 +21535,7 @@
         <v>88</v>
       </c>
       <c r="B2" s="69">
-        <f>'[5]CU énergie'!$H48</f>
+        <f>'[4]CU énergie'!$H48</f>
         <v>21.052878725363069</v>
       </c>
       <c r="C2" s="69">
@@ -21762,35 +21572,35 @@
         <v>89</v>
       </c>
       <c r="B3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="C3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="D3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="E3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="F3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="G3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="H3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
       <c r="I3" s="69">
-        <f>'[5]CU énergie'!$H49</f>
+        <f>'[4]CU énergie'!$H49</f>
         <v>4.6192271301325709</v>
       </c>
     </row>
@@ -21799,35 +21609,35 @@
         <v>90</v>
       </c>
       <c r="B4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="C4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="D4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="E4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="F4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="G4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="H4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
       <c r="I4" s="69">
-        <f>'[5]CU énergie'!$H50</f>
+        <f>'[4]CU énergie'!$H50</f>
         <v>2.7715362780795427</v>
       </c>
     </row>
@@ -21836,35 +21646,35 @@
         <v>91</v>
       </c>
       <c r="B5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="C5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="D5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="E5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="F5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="G5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="H5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
       <c r="I5" s="69">
-        <f>'[5]CU énergie'!$H51</f>
+        <f>'[4]CU énergie'!$H51</f>
         <v>8.3146088342386282</v>
       </c>
     </row>
@@ -21873,7 +21683,7 @@
         <v>92</v>
       </c>
       <c r="B6" s="69">
-        <f>'[5]CU énergie'!$H52</f>
+        <f>'[4]CU énergie'!$H52</f>
         <v>12.9338359643712</v>
       </c>
       <c r="C6" s="69">
@@ -21910,7 +21720,7 @@
         <v>93</v>
       </c>
       <c r="B7" s="69">
-        <f>'[5]CU énergie'!$H53</f>
+        <f>'[4]CU énergie'!$H53</f>
         <v>62.140352394535242</v>
       </c>
       <c r="C7" s="69">
@@ -21947,35 +21757,35 @@
         <v>94</v>
       </c>
       <c r="B8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="C8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="D8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="E8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="F8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="G8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="H8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
       <c r="I8" s="69">
-        <f>'[5]CU énergie'!$H54</f>
+        <f>'[4]CU énergie'!$H54</f>
         <v>17</v>
       </c>
     </row>
@@ -21984,35 +21794,35 @@
         <v>95</v>
       </c>
       <c r="B9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="C9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="D9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="E9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="F9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="G9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="H9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
       <c r="I9" s="69">
-        <f>'[5]CU énergie'!$H55</f>
+        <f>'[4]CU énergie'!$H55</f>
         <v>23.4</v>
       </c>
     </row>
@@ -22600,127 +22410,127 @@
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="D3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="E3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="F3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="G3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="H3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="I3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="J3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="K3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="L3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="M3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="N3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="O3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="P3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="Q3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="R3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="S3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="T3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="U3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="V3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="W3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="X3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="Y3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="Z3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AA3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AB3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AC3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AD3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AE3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AF3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AG3" s="69">
-        <f>'[5]CU énergie'!$F49*1</f>
+        <f>'[4]CU énergie'!$F49*1</f>
         <v>122.57599999999999</v>
       </c>
       <c r="AH3" s="41"/>
@@ -22754,7 +22564,7 @@
       </c>
       <c r="B4" s="69"/>
       <c r="C4" s="69">
-        <f>'[5]CU énergie'!$F50*'coût TEND'!C80*'coût TEND'!C78</f>
+        <f>'[4]CU énergie'!$F50*'coût TEND'!C80*'coût TEND'!C78</f>
         <v>7592.664403321055</v>
       </c>
       <c r="D4" s="69">
@@ -22908,127 +22718,127 @@
       </c>
       <c r="B5" s="69"/>
       <c r="C5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="D5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="E5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="F5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="G5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="H5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="I5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="J5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="K5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="L5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="M5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="N5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="O5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="P5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="Q5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="R5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="S5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="T5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="U5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="V5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="W5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="X5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="Y5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="Z5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AA5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AB5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AC5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AD5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AE5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AF5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AG5" s="69">
-        <f>'[5]CU énergie'!$F51*10</f>
+        <f>'[4]CU énergie'!$F51*10</f>
         <v>143.1960410341097</v>
       </c>
       <c r="AH5" s="41"/>
@@ -23370,7 +23180,7 @@
       </c>
       <c r="B8" s="69"/>
       <c r="C8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût TEND'!C128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût TEND'!C128*40</f>
         <v>39954.327247697649</v>
       </c>
       <c r="D8" s="69">
@@ -23390,7 +23200,7 @@
         <v>40238.184753178466</v>
       </c>
       <c r="H8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût TEND'!D128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût TEND'!D128*40</f>
         <v>40309.149129548685</v>
       </c>
       <c r="I8" s="69">
@@ -23410,7 +23220,7 @@
         <v>40903.162343345983</v>
       </c>
       <c r="M8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût TEND'!E128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût TEND'!E128*40</f>
         <v>41051.665646795293</v>
       </c>
       <c r="N8" s="69">
@@ -23430,7 +23240,7 @@
         <v>40599.288506085191</v>
       </c>
       <c r="R8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût TEND'!F128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût TEND'!F128*40</f>
         <v>40486.194220907681</v>
       </c>
       <c r="S8" s="69">
@@ -23450,7 +23260,7 @@
         <v>40033.817080197608</v>
       </c>
       <c r="W8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût TEND'!G128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût TEND'!G128*40</f>
         <v>39920.722795020076</v>
       </c>
       <c r="X8" s="69">
@@ -23470,7 +23280,7 @@
         <v>39468.345654309975</v>
       </c>
       <c r="AB8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût TEND'!H128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût TEND'!H128*40</f>
         <v>39355.251369132464</v>
       </c>
       <c r="AC8" s="69">
@@ -23490,7 +23300,7 @@
         <v>38902.874228422363</v>
       </c>
       <c r="AG8" s="69">
-        <f>'[5]CU énergie'!$F54*'coût TEND'!I128*40</f>
+        <f>'[4]CU énergie'!$F54*'coût TEND'!I128*40</f>
         <v>38789.779943244837</v>
       </c>
       <c r="AH8" s="41"/>
@@ -23524,7 +23334,7 @@
       </c>
       <c r="B9" s="69"/>
       <c r="C9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 AMS'!$I$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 AMS'!$I$12*20</f>
         <v>6108.6583217156422</v>
       </c>
       <c r="D9" s="69">
@@ -23544,7 +23354,7 @@
         <v>11050.95268897023</v>
       </c>
       <c r="H9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 '!$N$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 '!$N$12*20</f>
         <v>12286.526280783877</v>
       </c>
       <c r="I9" s="69">
@@ -23564,7 +23374,7 @@
         <v>14254.74857499461</v>
       </c>
       <c r="M9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 '!S$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 '!S$12*20</f>
         <v>14746.80414854729</v>
       </c>
       <c r="N9" s="69">
@@ -23584,7 +23394,7 @@
         <v>15855.835490739915</v>
       </c>
       <c r="R9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 '!X$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 '!X$12*20</f>
         <v>16133.093326288075</v>
       </c>
       <c r="S9" s="69">
@@ -23604,7 +23414,7 @@
         <v>20407.9593212379</v>
       </c>
       <c r="W9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 '!AC$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 '!AC$12*20</f>
         <v>21476.675819975357</v>
       </c>
       <c r="X9" s="69">
@@ -23624,7 +23434,7 @@
         <v>22709.998895529487</v>
       </c>
       <c r="AB9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 '!AH$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 '!AH$12*20</f>
         <v>23018.329664418023</v>
       </c>
       <c r="AC9" s="69">
@@ -23644,7 +23454,7 @@
         <v>24294.342935020832</v>
       </c>
       <c r="AG9" s="69">
-        <f>'[5]CU énergie'!$F55*'[7]Cibles ThreeME v2 '!AM$12*20</f>
+        <f>'[4]CU énergie'!$F55*'[6]Cibles ThreeME v2 '!AM$12*20</f>
         <v>24613.34625267153</v>
       </c>
       <c r="AH9" s="41"/>
@@ -25700,7 +25510,7 @@
         <v>7275.7217944861814</v>
       </c>
       <c r="D13" s="90">
-        <f>[6]NUCLEAIRE!$JW$316</f>
+        <f>[5]NUCLEAIRE!$JW$316</f>
         <v>7280.6399999999994</v>
       </c>
       <c r="E13" s="74"/>
@@ -25715,7 +25525,7 @@
         <v>4234.3494632002576</v>
       </c>
       <c r="M13" s="90">
-        <f>[6]NUCLEAIRE!$KG$612</f>
+        <f>[5]NUCLEAIRE!$KG$612</f>
         <v>5384.0850731707314</v>
       </c>
       <c r="N13" s="74"/>
@@ -25741,7 +25551,7 @@
         <v>1358.3768919087909</v>
       </c>
       <c r="AG13" s="90">
-        <f>[6]NUCLEAIRE!$LA$612</f>
+        <f>[5]NUCLEAIRE!$LA$612</f>
         <v>300.51422138836773</v>
       </c>
       <c r="AH13" s="75"/>
@@ -25751,7 +25561,7 @@
         <v>33926.772434118495</v>
       </c>
       <c r="AK13" s="96">
-        <f>SUM([6]NUCLEAIRE!$JX$612:$KB$612)</f>
+        <f>SUM([5]NUCLEAIRE!$JX$612:$KB$612)</f>
         <v>21239.585466537508</v>
       </c>
       <c r="AL13" s="95">
@@ -25759,7 +25569,7 @@
         <v>41765.723337404095</v>
       </c>
       <c r="AM13" s="96">
-        <f>SUM([6]NUCLEAIRE!$KH$612:$LA$612)</f>
+        <f>SUM([5]NUCLEAIRE!$KH$612:$LA$612)</f>
         <v>36527.759729831145</v>
       </c>
       <c r="AN13" s="95">
@@ -25767,7 +25577,7 @@
         <v>90008.109207917601</v>
       </c>
       <c r="AO13" s="96">
-        <f>SUM([6]NUCLEAIRE!$JX$612:$LA$612)</f>
+        <f>SUM([5]NUCLEAIRE!$JX$612:$LA$612)</f>
         <v>81663.789293929643</v>
       </c>
       <c r="AP13" s="75"/>
@@ -25876,7 +25686,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="D15" s="89">
-        <f>+[6]PRODELEC!$N$2226</f>
+        <f>+[5]PRODELEC!$N$2226</f>
         <v>376.49738567366785</v>
       </c>
       <c r="E15" s="74"/>
@@ -25891,7 +25701,7 @@
         <v>110.6358164700559</v>
       </c>
       <c r="M15" s="89">
-        <f>++[6]PRODELEC!$KG$2226</f>
+        <f>++[5]PRODELEC!$KG$2226</f>
         <v>0</v>
       </c>
       <c r="N15" s="74"/>
@@ -25917,7 +25727,7 @@
         <v>2203.8416757133036</v>
       </c>
       <c r="AG15" s="89">
-        <f>++[6]PRODELEC!$LA$2226</f>
+        <f>++[5]PRODELEC!$LA$2226</f>
         <v>0</v>
       </c>
       <c r="AH15" s="75"/>
@@ -25927,7 +25737,7 @@
         <v>2.5</v>
       </c>
       <c r="AK15" s="97">
-        <f>SUM([6]PRODELEC!$JX$2226:$KB$2226)</f>
+        <f>SUM([5]PRODELEC!$JX$2226:$KB$2226)</f>
         <v>0</v>
       </c>
       <c r="AL15" s="95">
@@ -25935,7 +25745,7 @@
         <v>11165.986264690431</v>
       </c>
       <c r="AM15" s="96">
-        <f>SUM([6]PRODELEC!$KH$2226:$LA$2226)</f>
+        <f>SUM([5]PRODELEC!$KH$2226:$LA$2226)</f>
         <v>0</v>
       </c>
       <c r="AN15" s="95">
@@ -25943,7 +25753,7 @@
         <v>11550.440227487657</v>
       </c>
       <c r="AO15" s="103">
-        <f>SUM([6]PRODELEC!$JX$2226:$LA$2226)</f>
+        <f>SUM([5]PRODELEC!$JX$2226:$LA$2226)</f>
         <v>0</v>
       </c>
       <c r="AP15" s="75"/>
@@ -26052,7 +25862,7 @@
         <v>3784.59385604311</v>
       </c>
       <c r="D17" s="90">
-        <f>[6]PRODELEC!$N$619+[6]PRODELEC!$N$1188</f>
+        <f>[5]PRODELEC!$N$619+[5]PRODELEC!$N$1188</f>
         <v>3074.4563903529388</v>
       </c>
       <c r="E17" s="74"/>
@@ -26067,7 +25877,7 @@
         <v>4048.7068799999929</v>
       </c>
       <c r="M17" s="90">
-        <f>[6]PRODELEC!$KG$619+[6]PRODELEC!$KG$1188</f>
+        <f>[5]PRODELEC!$KG$619+[5]PRODELEC!$KG$1188</f>
         <v>2925.4843887459215</v>
       </c>
       <c r="N17" s="74"/>
@@ -26093,7 +25903,7 @@
         <v>4847.0857169590727</v>
       </c>
       <c r="AG17" s="90">
-        <f>[6]PRODELEC!$LA$619+[6]PRODELEC!$LA$1188</f>
+        <f>[5]PRODELEC!$LA$619+[5]PRODELEC!$LA$1188</f>
         <v>4138.7290918005183</v>
       </c>
       <c r="AH17" s="75"/>
@@ -26103,7 +25913,7 @@
         <v>16770.854868866722</v>
       </c>
       <c r="AK17" s="98">
-        <f>SUM([6]PRODELEC!$JX$619:$KB$619)+SUM([6]PRODELEC!$JX$1188:$KB$1188)</f>
+        <f>SUM([5]PRODELEC!$JX$619:$KB$619)+SUM([5]PRODELEC!$JX$1188:$KB$1188)</f>
         <v>20459.900081406297</v>
       </c>
       <c r="AL17" s="95">
@@ -26111,7 +25921,7 @@
         <v>78068.943269493291</v>
       </c>
       <c r="AM17" s="98">
-        <f>SUM([6]PRODELEC!$KH$619:$LA$619)+SUM([6]PRODELEC!$KH$1188:$LA$1188)</f>
+        <f>SUM([5]PRODELEC!$KH$619:$LA$619)+SUM([5]PRODELEC!$KH$1188:$LA$1188)</f>
         <v>68629.122621652888</v>
       </c>
       <c r="AN17" s="95">
@@ -26119,7 +25929,7 @@
         <v>107772.91629442244</v>
       </c>
       <c r="AO17" s="98">
-        <f>SUM([6]PRODELEC!$JX$619:$LA$619)+SUM([6]PRODELEC!$JX$1188:$LA$1188)</f>
+        <f>SUM([5]PRODELEC!$JX$619:$LA$619)+SUM([5]PRODELEC!$JX$1188:$LA$1188)</f>
         <v>104689.44975734083</v>
       </c>
       <c r="AP17" s="74"/>
@@ -26149,7 +25959,7 @@
         <v>2032.2964148225478</v>
       </c>
       <c r="D18" s="90">
-        <f>SUM([6]PRODELEC!$N$1734:$N$1736)</f>
+        <f>SUM([5]PRODELEC!$N$1734:$N$1736)</f>
         <v>2636.463615903976</v>
       </c>
       <c r="E18" s="74"/>
@@ -26164,7 +25974,7 @@
         <v>1518.3561477012531</v>
       </c>
       <c r="M18" s="90">
-        <f>[6]PRODELEC!$KG$1796</f>
+        <f>[5]PRODELEC!$KG$1796</f>
         <v>1893.3198547847046</v>
       </c>
       <c r="N18" s="74"/>
@@ -26190,7 +26000,7 @@
         <v>2034.1807321515639</v>
       </c>
       <c r="AG18" s="90">
-        <f>[6]PRODELEC!$LA$1796</f>
+        <f>[5]PRODELEC!$LA$1796</f>
         <v>3626.9615298810877</v>
       </c>
       <c r="AH18" s="75"/>
@@ -26200,7 +26010,7 @@
         <v>9080.7352472660223</v>
       </c>
       <c r="AK18" s="98">
-        <f>SUM([6]PRODELEC!$JX$1796:$KB$1796)</f>
+        <f>SUM([5]PRODELEC!$JX$1796:$KB$1796)</f>
         <v>12669.159878414404</v>
       </c>
       <c r="AL18" s="95">
@@ -26208,7 +26018,7 @@
         <v>44244.581935071845</v>
       </c>
       <c r="AM18" s="98">
-        <f>SUM([6]PRODELEC!$KH$1796:$LA$1796)</f>
+        <f>SUM([5]PRODELEC!$KH$1796:$LA$1796)</f>
         <v>64525.217657442197</v>
       </c>
       <c r="AN18" s="95">
@@ -26216,7 +26026,7 @@
         <v>58204.391607196783</v>
       </c>
       <c r="AO18" s="98">
-        <f>SUM([6]PRODELEC!$JX$1796:$LA$1796)</f>
+        <f>SUM([5]PRODELEC!$JX$1796:$LA$1796)</f>
         <v>87551.579056891293</v>
       </c>
       <c r="AP18" s="74"/>
@@ -26246,7 +26056,7 @@
         <v>1273.0888434995527</v>
       </c>
       <c r="D19" s="82">
-        <f>[6]PRODELEC!$N$247</f>
+        <f>[5]PRODELEC!$N$247</f>
         <v>740.67857917962817</v>
       </c>
       <c r="E19" s="74"/>
@@ -26261,7 +26071,7 @@
         <v>1393.5880108192237</v>
       </c>
       <c r="M19" s="82">
-        <f>[6]PRODELEC!$KG$247</f>
+        <f>[5]PRODELEC!$KG$247</f>
         <v>0</v>
       </c>
       <c r="N19" s="74"/>
@@ -26287,7 +26097,7 @@
         <v>1022.7783089343081</v>
       </c>
       <c r="AG19" s="82">
-        <f>[6]PRODELEC!$LA$247</f>
+        <f>[5]PRODELEC!$LA$247</f>
         <v>0</v>
       </c>
       <c r="AH19" s="75"/>
@@ -26297,7 +26107,7 @@
         <v>5366.853881905794</v>
       </c>
       <c r="AK19" s="98">
-        <f>SUM([6]PRODELEC!$JX$247:$KB$247)</f>
+        <f>SUM([5]PRODELEC!$JX$247:$KB$247)</f>
         <v>262.5320704580422</v>
       </c>
       <c r="AL19" s="95">
@@ -26305,7 +26115,7 @@
         <v>18897.831627286934</v>
       </c>
       <c r="AM19" s="98">
-        <f>SUM([6]PRODELEC!$KH$247:$LA$247)</f>
+        <f>SUM([5]PRODELEC!$KH$247:$LA$247)</f>
         <v>0</v>
       </c>
       <c r="AN19" s="95">
@@ -26313,7 +26123,7 @@
         <v>28911.889131462296</v>
       </c>
       <c r="AO19" s="98">
-        <f>SUM([6]PRODELEC!$JX$247:$LA$247)</f>
+        <f>SUM([5]PRODELEC!$JX$247:$LA$247)</f>
         <v>262.5320704580422</v>
       </c>
       <c r="AP19" s="74"/>
@@ -26343,7 +26153,7 @@
         <v>1833.7977444003209</v>
       </c>
       <c r="D20" s="90">
-        <f>[6]PRODELEC!$N$2163</f>
+        <f>[5]PRODELEC!$N$2163</f>
         <v>172.81430065449953</v>
       </c>
       <c r="E20" s="74"/>
@@ -26358,7 +26168,7 @@
         <v>1433.703672739869</v>
       </c>
       <c r="M20" s="90">
-        <f>[6]PRODELEC!$KG$2163</f>
+        <f>[5]PRODELEC!$KG$2163</f>
         <v>0</v>
       </c>
       <c r="N20" s="74"/>
@@ -26384,7 +26194,7 @@
         <v>1825.1273526380708</v>
       </c>
       <c r="AG20" s="90">
-        <f>[6]PRODELEC!$LA$2163</f>
+        <f>[5]PRODELEC!$LA$2163</f>
         <v>0</v>
       </c>
       <c r="AH20" s="75"/>
@@ -26394,7 +26204,7 @@
         <v>8322.8193354039704</v>
       </c>
       <c r="AK20" s="102">
-        <f>SUM([6]PRODELEC!$JX$2163:$KB$2163)</f>
+        <f>SUM([5]PRODELEC!$JX$2163:$KB$2163)</f>
         <v>0</v>
       </c>
       <c r="AL20" s="101">
@@ -26402,7 +26212,7 @@
         <v>30901.715056646273</v>
       </c>
       <c r="AM20" s="102">
-        <f>SUM([6]PRODELEC!$KH$2163:$LA$2163)</f>
+        <f>SUM([5]PRODELEC!$KH$2163:$LA$2163)</f>
         <v>0</v>
       </c>
       <c r="AN20" s="101">
@@ -26410,7 +26220,7 @@
         <v>43797.678614483557</v>
       </c>
       <c r="AO20" s="102">
-        <f>SUM([6]PRODELEC!$JX$2163:$LA$2163)</f>
+        <f>SUM([5]PRODELEC!$JX$2163:$LA$2163)</f>
         <v>0</v>
       </c>
       <c r="AP20" s="75"/>
